--- a/runs/RELX/2026-10-14/bear/scratch/g_rf_fisher/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/g_rf_fisher/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2087.217273725546</v>
+        <v>2146.645254310542</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.098021</v>
+        <v>0.09023780000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.09103535304496001</v>
+        <v>0.08424980362096002</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11257.151032752</v>
+        <v>11429.41408892585</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>40532.93748609715</v>
+        <v>44813.70155246527</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>27386.30079065329</v>
+        <v>31140.72596654746</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>38643.45182340528</v>
+        <v>42570.14005547331</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>31646.45182340528</v>
+        <v>35573.14005547331</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>30779.05698477081</v>
+        <v>34791.49388251898</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>17.65102425713499</v>
+        <v>19.95205710058498</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1765.102425713499</v>
+        <v>1995.205710058498</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.3630088684</v>
+        <v>-0.2799690689</v>
       </c>
     </row>
   </sheetData>
